--- a/artfynd/A 27867-2023 artfynd.xlsx
+++ b/artfynd/A 27867-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 27867-2023 artfynd.xlsx
+++ b/artfynd/A 27867-2023 artfynd.xlsx
@@ -10051,7 +10051,7 @@
         <v>112270965</v>
       </c>
       <c r="B93" t="n">
-        <v>90185</v>
+        <v>90195</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>

--- a/artfynd/A 27867-2023 artfynd.xlsx
+++ b/artfynd/A 27867-2023 artfynd.xlsx
@@ -10051,7 +10051,7 @@
         <v>112270965</v>
       </c>
       <c r="B93" t="n">
-        <v>90195</v>
+        <v>90207</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>

--- a/artfynd/A 27867-2023 artfynd.xlsx
+++ b/artfynd/A 27867-2023 artfynd.xlsx
@@ -10051,7 +10051,7 @@
         <v>112270965</v>
       </c>
       <c r="B93" t="n">
-        <v>90207</v>
+        <v>90208</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>

--- a/artfynd/A 27867-2023 artfynd.xlsx
+++ b/artfynd/A 27867-2023 artfynd.xlsx
@@ -10051,7 +10051,7 @@
         <v>112270965</v>
       </c>
       <c r="B93" t="n">
-        <v>90208</v>
+        <v>90211</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>

--- a/artfynd/A 27867-2023 artfynd.xlsx
+++ b/artfynd/A 27867-2023 artfynd.xlsx
@@ -10051,7 +10051,7 @@
         <v>112270965</v>
       </c>
       <c r="B93" t="n">
-        <v>90211</v>
+        <v>90217</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>

--- a/artfynd/A 27867-2023 artfynd.xlsx
+++ b/artfynd/A 27867-2023 artfynd.xlsx
@@ -10051,7 +10051,7 @@
         <v>112270965</v>
       </c>
       <c r="B93" t="n">
-        <v>90217</v>
+        <v>90218</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>

--- a/artfynd/A 27867-2023 artfynd.xlsx
+++ b/artfynd/A 27867-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY113"/>
+  <dimension ref="A1:AY114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12294,6 +12294,132 @@
         </is>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>123021203</v>
+      </c>
+      <c r="B114" t="n">
+        <v>96225</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>1841</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Vedflikmossa</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Lophozia guttulata</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Frebbenboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>664847</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6698983</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Med svepen. Stora tydliga trigoner.</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL114" t="inlineStr">
+        <is>
+          <t>Låga</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Låga</t>
+        </is>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27867-2023 artfynd.xlsx
+++ b/artfynd/A 27867-2023 artfynd.xlsx
@@ -12299,7 +12299,7 @@
         <v>123021203</v>
       </c>
       <c r="B114" t="n">
-        <v>96225</v>
+        <v>96233</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>

--- a/artfynd/A 27867-2023 artfynd.xlsx
+++ b/artfynd/A 27867-2023 artfynd.xlsx
@@ -12299,7 +12299,7 @@
         <v>123021203</v>
       </c>
       <c r="B114" t="n">
-        <v>96233</v>
+        <v>96236</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>

--- a/artfynd/A 27867-2023 artfynd.xlsx
+++ b/artfynd/A 27867-2023 artfynd.xlsx
@@ -12299,7 +12299,7 @@
         <v>123021203</v>
       </c>
       <c r="B114" t="n">
-        <v>96236</v>
+        <v>96238</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>

--- a/artfynd/A 27867-2023 artfynd.xlsx
+++ b/artfynd/A 27867-2023 artfynd.xlsx
@@ -12299,7 +12299,7 @@
         <v>123021203</v>
       </c>
       <c r="B114" t="n">
-        <v>96238</v>
+        <v>96244</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>

--- a/artfynd/A 27867-2023 artfynd.xlsx
+++ b/artfynd/A 27867-2023 artfynd.xlsx
@@ -12299,7 +12299,7 @@
         <v>123021203</v>
       </c>
       <c r="B114" t="n">
-        <v>96247</v>
+        <v>96264</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
